--- a/astro-site/public/dl/burger-joint-checklist-templates/02-burger-kitchen-station-checklists.xlsx
+++ b/astro-site/public/dl/burger-joint-checklist-templates/02-burger-kitchen-station-checklists.xlsx
@@ -998,9 +998,9 @@
       <c r="A10" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="26" t="inlineStr">
-        <is>
-          <t>Check spatulas, presses, thermometer</t>
+      <c r="B10" s="33" t="inlineStr">
+        <is>
+          <t>Check spatulas, presses and the probe thermometer: ice-point check (32 °F), recalibrate if it's off</t>
         </is>
       </c>
       <c r="C10" s="27" t="inlineStr">
@@ -1173,9 +1173,9 @@
       <c r="A17" s="25" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="26" t="inlineStr">
-        <is>
-          <t>Keep the griddle clean between batches (scraper)</t>
+      <c r="B17" s="33" t="inlineStr">
+        <is>
+          <t>Keep the griddle clean between batches (scraper); wash, rinse and sanitize spatulas, press and tongs at least every 4 h during service, or swap in clean ones (FDA 4-602.11)</t>
         </is>
       </c>
       <c r="C17" s="27" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="B6" s="33" t="inlineStr">
         <is>
-          <t>Set up inserts: lettuce, tomato, onion and pickles — raw-eaten produce washed under running potable water (FDA 3-302.15); if using a produce wash, only one approved for fruits and vegetables, at label dose, then RINSE. Inserts in the make-line cooler at 41 °F or below (FDA 3-501.16)</t>
+          <t>Set up inserts: lettuce, tomato, onion and pickles — raw-eaten produce washed under running potable water (FDA 3-302.15); if using a produce wash, only one approved for fruits and vegetables, at label dose, then RINSE. Inserts in the make-line cooler at 41 °F or below (FDA 3-501.16) — log reading: ____ °F</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="B18" s="26" t="inlineStr">
         <is>
-          <t>Turn off the fryer and let it cool</t>
+          <t>Turn off the fryer at the end of service</t>
         </is>
       </c>
       <c r="C18" s="27" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="B19" s="34" t="inlineStr">
         <is>
-          <t>Filter or change the oil if dark or smelly, as the fryer manufacturer says (many filter hot by design, others need to cool first); heat-resistant gloves, apron and goggles</t>
+          <t>Filter the oil every night as the fryer manufacturer says (built-in filtration usually runs with the oil still hot, right after service; a portable filter only once it has cooled to what the manual allows) and change it when the TPM tester says; heat-resistant gloves, apron and goggles</t>
         </is>
       </c>
       <c r="C19" s="27" t="inlineStr">
